--- a/inventory/files/2026-W40/STA_US_AUTO_2026-W40.xlsx
+++ b/inventory/files/2026-W40/STA_US_AUTO_2026-W40.xlsx
@@ -1536,7 +1536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="17"/>
   <cols>
     <col width="26.5" customWidth="1" style="28" min="1" max="1"/>
@@ -1692,69 +1692,69 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>67515</v>
+        <v>72240</v>
       </c>
       <c r="C9" t="n">
         <v>105</v>
       </c>
       <c r="D9" t="n">
-        <v>643</v>
+        <v>688</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AH-TRKITA</t>
+          <t>AH-RCPL-B14A</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8616</v>
+        <v>6828</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AH-RCPAINTA</t>
+          <t>AH-RCTIRE10A</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5730</v>
+        <v>5433</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AH-RCTIRE10A</t>
+          <t>AH-RCPAINTA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4614</v>
+        <v>4294</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AH-RCPL-B14A</t>
+          <t>AH-GLASSCOATA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3409</v>
+        <v>2400</v>
+      </c>
+      <c r="C13" t="n">
+        <v>150</v>
+      </c>
+      <c r="D13" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AH-GLASSCOATA</t>
+          <t>AH-VEHSHAM32A</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2100</v>
-      </c>
-      <c r="C14" t="n">
-        <v>150</v>
-      </c>
-      <c r="D14" t="n">
-        <v>14</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="15">
@@ -1764,59 +1764,65 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1590</v>
+        <v>1080</v>
       </c>
       <c r="C15" t="n">
         <v>30</v>
       </c>
       <c r="D15" t="n">
-        <v>53</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AH-RCWHL14A</t>
+          <t>AH-PROPAINTKITA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1039</v>
+        <v>896</v>
+      </c>
+      <c r="C16" t="n">
+        <v>8</v>
+      </c>
+      <c r="D16" t="n">
+        <v>112</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AH-PROPAINTKITA</t>
+          <t>AH-MICRTOWEL12A</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>992</v>
+        <v>840</v>
       </c>
       <c r="C17" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>124</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AH-SPONGE3A</t>
+          <t>AH-RCWHL14A</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>920</v>
+        <v>777</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AH-VEHSHAM32A</t>
+          <t>AH-SPONGE3A</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>901</v>
+        <v>667</v>
       </c>
     </row>
     <row r="20">
@@ -1826,7 +1832,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>714</v>
+        <v>606</v>
       </c>
     </row>
     <row r="21">
@@ -1836,7 +1842,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>550</v>
+        <v>596</v>
       </c>
     </row>
     <row r="22">
@@ -1846,65 +1852,59 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>465</v>
+        <v>557</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AH-RCPV14A</t>
+          <t>AH-REPAIRHL</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>300</v>
+        <v>207</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AH-810A</t>
+          <t>AH-813A</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>266</v>
+        <v>150</v>
       </c>
       <c r="C24" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="D24" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AH-PROWHLKITA</t>
+          <t>AH-RCINT14-2PA</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>240</v>
+        <v>144</v>
       </c>
       <c r="C25" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D25" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AH-MICRTOWEL12A</t>
+          <t>AH-RCPAINTQA</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>240</v>
-      </c>
-      <c r="C26" t="n">
-        <v>40</v>
-      </c>
-      <c r="D26" t="n">
-        <v>6</v>
+        <v>144</v>
       </c>
     </row>
     <row r="27">
@@ -1914,84 +1914,84 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>240</v>
+        <v>120</v>
       </c>
       <c r="C27" t="n">
         <v>120</v>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AH-813A</t>
+          <t>AH-RCINT-QA</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>210</v>
+        <v>80</v>
       </c>
       <c r="C28" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D28" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AH-REPAIRHL</t>
+          <t>AH-VEHSHAM16A</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>155</v>
+        <v>78</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AH-RCINT14-2PA</t>
+          <t>AH-PROMARKITA</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>132</v>
+        <v>32</v>
       </c>
       <c r="C30" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D30" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AH-RCINT-QA</t>
+          <t>AH-811A</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>100</v>
+        <v>28</v>
       </c>
       <c r="C31" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D31" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AH-CLAYMITTA</t>
+          <t>AH-MFDRYTWLA</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="C32" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="D32" t="n">
         <v>1</v>
@@ -2000,148 +2000,26 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AH-GCLEAN-B16A</t>
+          <t>AH-BNDL-COREA</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="n">
         <v>20</v>
-      </c>
-      <c r="D33" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AH-RCPV-QA</t>
+          <t>AH-PRORV12</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>AH-811A</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>28</v>
-      </c>
-      <c r="C35" t="n">
-        <v>14</v>
-      </c>
-      <c r="D35" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>AH-MFDRYTWLA</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>25</v>
-      </c>
-      <c r="C36" t="n">
-        <v>25</v>
-      </c>
-      <c r="D36" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>AH-RCINT14A</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>20</v>
-      </c>
-      <c r="C37" t="n">
-        <v>20</v>
-      </c>
-      <c r="D37" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>AH-BNDL-PROA</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>15</v>
-      </c>
-      <c r="C38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D38" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>AH-BNDL-COREA</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>8</v>
-      </c>
-      <c r="C39" t="n">
-        <v>1</v>
-      </c>
-      <c r="D39" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>AH-PROMARKITA</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>8</v>
-      </c>
-      <c r="C40" t="n">
-        <v>8</v>
-      </c>
-      <c r="D40" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>AH-PROPVKITA</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>8</v>
-      </c>
-      <c r="C41" t="n">
-        <v>8</v>
-      </c>
-      <c r="D41" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>AH-PRORV12</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
         <v>3</v>
       </c>
     </row>

--- a/inventory/files/2026-W40/STA_US_AUTO_2026-W40.xlsx
+++ b/inventory/files/2026-W40/STA_US_AUTO_2026-W40.xlsx
@@ -1692,13 +1692,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>72240</v>
+        <v>71820</v>
       </c>
       <c r="C9" t="n">
         <v>105</v>
       </c>
       <c r="D9" t="n">
-        <v>688</v>
+        <v>684</v>
       </c>
     </row>
     <row r="10">
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6828</v>
+        <v>6742</v>
       </c>
     </row>
     <row r="11">
@@ -1718,7 +1718,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5433</v>
+        <v>5211</v>
       </c>
     </row>
     <row r="12">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4294</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="13">
@@ -1754,7 +1754,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1790</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="15">
@@ -1764,13 +1764,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1080</v>
+        <v>1050</v>
       </c>
       <c r="C15" t="n">
         <v>30</v>
       </c>
       <c r="D15" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -1780,39 +1780,39 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>896</v>
+        <v>888</v>
       </c>
       <c r="C16" t="n">
         <v>8</v>
       </c>
       <c r="D16" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AH-MICRTOWEL12A</t>
+          <t>AH-RCWHL14A</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>840</v>
-      </c>
-      <c r="C17" t="n">
-        <v>40</v>
-      </c>
-      <c r="D17" t="n">
-        <v>21</v>
+        <v>762</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AH-RCWHL14A</t>
+          <t>AH-MICRTOWEL12A</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>777</v>
+        <v>760</v>
+      </c>
+      <c r="C18" t="n">
+        <v>40</v>
+      </c>
+      <c r="D18" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="19">
@@ -1822,7 +1822,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>667</v>
+        <v>644</v>
       </c>
     </row>
     <row r="20">
@@ -1832,7 +1832,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>606</v>
+        <v>600</v>
       </c>
     </row>
     <row r="21">
@@ -1842,7 +1842,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>596</v>
+        <v>586</v>
       </c>
     </row>
     <row r="22">
@@ -1852,7 +1852,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>557</v>
+        <v>550</v>
       </c>
     </row>
     <row r="23">
@@ -1862,49 +1862,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AH-813A</t>
+          <t>AH-RCINT14-2PA</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="C24" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="D24" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AH-RCINT14-2PA</t>
+          <t>AH-RCPAINTQA</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>144</v>
-      </c>
-      <c r="C25" t="n">
-        <v>12</v>
-      </c>
-      <c r="D25" t="n">
-        <v>12</v>
+        <v>132</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AH-RCPAINTQA</t>
+          <t>AH-813A</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>144</v>
+        <v>120</v>
+      </c>
+      <c r="C26" t="n">
+        <v>30</v>
+      </c>
+      <c r="D26" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -1946,7 +1946,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>78</v>
+        <v>64</v>
       </c>
     </row>
     <row r="30">
